--- a/01_경혈별_해부생리_분석보고서/LU_수태음폐경/LU09_태연/LU09_태연_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/LU_수태음폐경/LU09_태연/LU09_태연_해부생리_분석데이터.xlsx
@@ -7,11 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.문헌스크리닝_원천분리" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.2대교재_해부구조_대조" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.3D좌표_Layer1~5_심도" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.생의학반사_BCheck_논문" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.ARI_v3.0_평가표" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구판_1.문헌스크리닝_원천분리" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구판_2.2대교재_해부구조_대조" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구판_3.3D좌표_Layer1~5_심도" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구판_4.생의학반사_BCheck_논문" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구판_5.ARI_v3.0_평가표" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARI_v3.0_이중채점" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Check_이중채점" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자침깊이_계산" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_LU9확인" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -584,6 +591,1109 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>중복제거</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:41:58</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:41:58</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:41:58</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:41:58</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>36</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>merged_into_existing=8 batch_dups=4; 'Taiyuan' 지명 오적중 다수</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>교재 용어</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FMA_ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FMA_label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>대응 수준</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>출처 교재</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>지배신경(FMA nerve_supply)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>상위 줄기(FMA)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>척수 분절</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>긴엄지벌림근 (abductor pollicis longus)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>38515</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Abductor pollicis longus</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FMA:80295 Nerve to abductor pollicis longus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Posterior interosseous nerve → Radial nerve</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>C7(primary/segmental), C8(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>위팔노근 (brachioradialis)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>38485</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Brachioradialis</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FMA:65334 Nerve to brachioradialis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Peripheral segment of radial nerve</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>C6(primary/segmental), C5(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>긴엄지폄근 (extensor pollicis longus)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>38521</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Extensor pollicis longus</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FMA:80289 Nerve to extensor pollicis longus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Posterior interosseous nerve → Radial nerve</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>C7(primary/segmental), C8(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>손등쪽 힘줄, 경로 밖</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>노쪽손목굽힘근 (flexor carpi radialis)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>38459</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Flexor carpi radialis</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FMA:44824 Nerve to flexor carpi radialis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Peripheral segment of median nerve</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C6(primary/segmental), C7(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>FMA 구획 오기(arm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>얕은손가락굽힘근 (flexor digitorum superficialis)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>38469</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Flexor digitorum superficialis</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FMA:44826 Nerve to flexor digitorum superficialis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Peripheral segment of median nerve</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>C8(primary/segmental), T1(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>근복은 아래팔 몸쪽(높이 밖)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>긴엄지굽힘근 (flexor pollicis longus)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>38481</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Flexor pollicis longus</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FMA:44830 Nerve to flexor pollicis longus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Anterior interosseous nerve → Peripheral segment of median nerve</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>C8(primary/segmental), C7(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FMA 구획 오기(arm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>네모엎침근 (pronator quadratus)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>38453</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pronator quadratus</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FMA:44835 Nerve to pronator quadratus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Anterior interosseous nerve → Peripheral segment of median nerve</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>C8(primary/segmental), C7(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>이 높이보다 몸쪽; FMA 구획 오기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>원엎침근 (pronator teres)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>38450</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pronator teres</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FMA:44823 Nerve to pronator teres</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Peripheral segment of median nerve</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>C7(primary/segmental), C6(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>근복은 아래팔 몸쪽(높이 밖)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>위팔노근의 힘줄 (tendon of the brachioradialis)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>40689</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tendon of brachioradialis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>노쪽손목굽힘근의 힘줄 (tendon of the flexor carpi radialis)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>38582</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tendon of flexor carpi radialis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>긴엄지굽힘근의 힘줄 (tendon of the flexor pollicis longus)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>38673</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tendon of flexor pollicis longus</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>손목굽힘근지지띠 (palmar carpal ligament)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FMA 미등재</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>가쪽아래팔피부신경 (lateral antebrachial cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>39080</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lateral cutaneous nerve of forearm</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>FMA:288511 Peripheral segment of musculocutaneous nerve</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>노신경의 얕은가지 (superficial branch of radial nerve); 노신경의 얕은가지 (superficial branch of the radial nerve)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>292885</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Superficial branch of radial nerve</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>FMA:37069 Radial nerve</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>덧노쪽피부정맥 (accessory cephalic vein)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>22970</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Accessory cephalic vein</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>FMA:13324 Cephalic vein → FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>노쪽피부정맥 (cephalic vein)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>13324</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cephalic vein</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>노동ㆍ정맥 (radial artery and vein)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>22730</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Radial artery</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>FMA:3951 Subclavian artery</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>자침점 동층 — SI 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>노동ㆍ정맥 (radial artery and vein)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>22947</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Radial vein</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>FMA:22934 Brachial vein → FMA:13329 Axillary vein → FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>분절 합집합</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>C5, C6, C7, C8, T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>교재 비교</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>공통 6 · 공통교재 단독 2 · 김재효 단독 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0, fma_query.py profile LU09 (2026-10-23). B1 보조(등록부 미등재)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>원래 내용</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>바꾼 내용</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>템플릿 초안(단일 채점 79.0 B, 범용 Layer mm, 무관 논문 9편)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tier 3 재작성: 원전 행 인용, 이중 채점 68.75±0 C, SI 50, B-Check 7/12 미부합, FMA·그림 4-1·8-1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>보고서 개정 이력 표</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1318,4 +2428,1425 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>지표</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>가중치</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>채점자 A</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>채점자 B</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>조정</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>루브릭 근거</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>근거 포인터</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S_orig ① 최초 기술</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>25점 차 조정</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>《本输》 위치+《明堂》 심도 vs 早期 '掌后' 모호</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>通考 L2225·2431·2299</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S_orig ② 후대 일치율</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>위치 일치, 동맥 표지·심도 분산</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>通鉴 L1053; 通考 L2209</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S_orig ③ 이명 해소</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>75</v>
+      </c>
+      <c r="D4" t="n">
+        <v>75</v>
+      </c>
+      <c r="E4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>피휘·오독·오귀속 연대순 해소</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>通考 L2205·2221·2473; KJH 행64</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S_orig ④ 通考 교감</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D5" t="n">
+        <v>75</v>
+      </c>
+      <c r="E5" t="n">
+        <v>75</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>동맥 표지·鱼际 별명 교정, 龙渊 미해결</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>通考 L2299·2361·2473</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S_orig (평균)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>①조정 후 75</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S_clarity</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C7" t="n">
+        <v>75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="n">
+        <v>75</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25점 차 조정</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>정위 표지·신경·혈관 일치, 근육 수록 높이 차이</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>교재 행62; FMA:22730·38459</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S_reflex</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>동물 연구만(LU9 단독·대조), 인체 다혈위 RCT, B-Check 7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>papers.id 2240·2238·2241·2244·1807·2237</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SI (S_safety)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>별도</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="n">
+        <v>75</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>25점 차 조정</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>노동맥 동층, 촉지 회피, 刺禁论·不宜用针</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>자침깊이 DB 행63; 通考 L2147·2437·2451</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ARI-Core</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>0.40×75+0.35×75+0.25×50</f>
+        <v/>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>68.75 ± 0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>등급 C</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>게이트 미적용</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>민감도(등가) 66.7 C 불변</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>표준 표기</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ARI v3.0 | ARI-Core 68.75 ± 0 (C) | SI 50 | 잠정 가중치 0.40/0.35/0.25 | 민감도(등가중치): 66.7 (C, 등급 불변)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>참조 ID</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>papers.id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>말초 실체</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>B1-01·B1-03·B1-04·B2-09 (+FMA)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>노동맥·노신경 얕은가지·LACN 일치, FMA exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>분절 정합</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>B1-02·B3-03·B3-05 (+FMA)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>C5~T1 vs 폐·심 T1~T4, T1만 겹침</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>구심 섬유·수용체</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>B3-06</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>LU9 특이 연구 없음, 유추</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>중추 경로</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>B3-12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LHA·FN DA/5-HT(쥐), PC5-6 rVLM 유추</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>원심·표적 효과</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>B3-05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2240·2238·2241·2244</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>폐 환기 개선 일치, 심장 효과 약함</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>인체 전환</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>B4-04·B4-05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1807·2237</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>다혈위 RCT만</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>미부합(&lt;8) → 가설, 동물 한정</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>문헌</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>푼</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mm(×2.3)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Layer(추정)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>황제명당경</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1~2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>刺入二分</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>침구갑을경</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1~2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>침구경험방</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1~2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>동의보감(동인)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1~2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>경락수혈학 공통교재</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3~5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6.9~11.5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>침구의학 공통교재</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3~5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6.9~11.5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>침구수혈통고</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3~5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6.9~11.5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>直刺0.3~0.5寸</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4·5·6판 针灸学(참고)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5~10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11.5~23.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2~5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7판에서 축소</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>针方六集(참고)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>不宜用针</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>자침깊이 DB 시트1 행 63 (N0=61). 금침 '0'·blank 없음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>papers.id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>저널</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PMID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>설계</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2240</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Zhen Ci Yan Jiu</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>35880273</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10.13702/j.1000-0607.20211299</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>동물, LU9 단독</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>폐손상 쥐 폐 환기 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2238</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Zhongguo Zhen Jiu</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>29231479</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.2017.02.013</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>동물, LU9 대조</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>太渊군 효과 뚜렷하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2241</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Zhen Ci Yan Jiu</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>29560633</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10.13702/j.1000-0607.170121</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>동물, LU9 대조</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HCN2, 심경&gt;폐경</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2244</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Acupunct Med</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>39579035</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10.1177/09645284241298716</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>동물, LU9-LU8 대조</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HT5-HT7 우세</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2235</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Zhongguo Zhen Jiu</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>34002567</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.20200509-k0001</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>동물, LU9+LU7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LHA/FN DA·5-HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2236</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Zhongguo Zhen Jiu</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>33068354</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.20190811-k0004</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>동물, LU9+LU7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NF-κB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2233</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zhongguo Zhen Jiu</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>36397226</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.20211201-k0004</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>동물, 다혈위</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>저산소</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Zhen Ci Yan Jiu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>30773865</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10.13702/j.1000-0607.180396</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>동물 해부 대응</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>쥐 경혈도</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1807</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ann Med</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>40953233</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10.1080/07853890.2025.2560684</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>인체 RCT, 다혈위</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VATS 폐합병증↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2237</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Zhongguo Zhen Jiu</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>32394654</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.20190412-0007</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>인체 RCT, 다혈위</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FEV1·PEF↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Zhongguo Zhen Jiu</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>29354929</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.2018.01.002</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>인체, 다혈위</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>천식</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2234</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Zhongguo Zhen Jiu</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>35272405</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.20210406-0004</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>인체, 다혈위</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>코로나 후유증</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2239</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Zhen Ci Yan Jiu</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>39433370</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10.13702/j.1000-0607.20230690</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>인체, 다혈위</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Photobiomodul Photomed Laser Surg</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>39446663</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10.1089/photob.2024.0106</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>인체, 다혈위</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>정중신경 전도</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Zhongguo Zhen Jiu</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>42116771</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.20250421-k0004</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>증례</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>